--- a/exports/red5-dhcp_commissioning.xlsx
+++ b/exports/red5-dhcp_commissioning.xlsx
@@ -587,7 +587,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27  ·  84 controllers  ·  1160 points</t>
+          <t>Generated 2026-07-30  ·  84 controllers  ·  1160 points</t>
         </is>
       </c>
     </row>
